--- a/data/trans_dic/IP19C05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,35</t>
+          <t>0,0; 9,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 8,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,92</t>
+          <t>0,0; 10,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,71</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,19</t>
+          <t>0,26; 2,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,14</t>
+          <t>0,65; 3,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,24</t>
+          <t>1,34; 5,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,31</t>
+          <t>0,54; 3,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,4</t>
+          <t>0,81; 3,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,56</t>
+          <t>0,64; 3,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,06</t>
+          <t>0,56; 2,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,02</t>
+          <t>0,88; 2,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,58</t>
+          <t>1,33; 3,7</t>
         </is>
       </c>
     </row>
@@ -897,32 +898,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,97</t>
+          <t>1,87; 10,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,39</t>
+          <t>0,79; 7,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,29</t>
+          <t>0,7; 5,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,2</t>
+          <t>1,81; 6,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,08</t>
+          <t>0,76; 4,32</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,09</t>
+          <t>0,36; 2,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,47</t>
+          <t>1,42; 4,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,15</t>
+          <t>1,36; 4,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,19</t>
+          <t>0,36; 2,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,1</t>
+          <t>0,78; 3,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,1</t>
+          <t>0,8; 3,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,74</t>
+          <t>0,52; 1,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,18</t>
+          <t>1,37; 3,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,12</t>
+          <t>1,37; 3,15</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4355</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3894</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2366</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4290</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4013</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3082</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1882</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7227</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4087</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4059</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11286</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>601; 5079</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1440; 8602</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3379; 12822</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1332; 7787</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1949; 8380</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1604; 8964</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2656; 10538</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4079; 13735</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6717; 18676</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3407</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2876</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1602; 8612</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4664</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>652; 5966</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>614; 5196</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3172</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3040; 11447</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1331; 7573</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9286</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6918</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15504</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>15257</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1266; 7840</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5024; 15210</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4915; 15038</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1317; 7925</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2840; 11182</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2928; 11394</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3691; 12639</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9897; 23270</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>10024; 23039</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Estudios-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,28</t>
+          <t>0,0; 9,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,69</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,22</t>
+          <t>0,26; 2,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,9</t>
+          <t>0,66; 3,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,07</t>
+          <t>1,42; 5,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,17</t>
+          <t>0,54; 3,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,48</t>
+          <t>0,61; 3,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,55</t>
+          <t>0,63; 3,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,22</t>
+          <t>0,54; 2,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,98</t>
+          <t>0,96; 3,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,7</t>
+          <t>1,3; 3,65</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,07</t>
+          <t>1,88; 10,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 5,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,26</t>
+          <t>0,8; 7,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,92</t>
+          <t>0,7; 7,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,83</t>
+          <t>1,9; 7,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,32</t>
+          <t>0,71; 3,99</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,23</t>
+          <t>0,35; 2,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,3</t>
+          <t>1,49; 4,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,15</t>
+          <t>1,45; 4,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,19</t>
+          <t>0,36; 2,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,06</t>
+          <t>0,78; 3,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,1</t>
+          <t>0,78; 3,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,77</t>
+          <t>0,49; 1,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,23</t>
+          <t>1,35; 3,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,15</t>
+          <t>1,24; 3,15</t>
         </is>
       </c>
     </row>
@@ -1306,17 +1306,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4355</t>
+          <t>0; 4607</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3894</t>
+          <t>0; 3845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2366</t>
+          <t>0; 2878</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4290</t>
+          <t>0; 3504</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4013</t>
+          <t>0; 3896</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3082</t>
+          <t>0; 3403</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>601; 5079</t>
+          <t>595; 5645</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1440; 8602</t>
+          <t>1458; 7949</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3379; 12822</t>
+          <t>3601; 12912</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1332; 7787</t>
+          <t>1336; 8005</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1949; 8380</t>
+          <t>1465; 8150</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1604; 8964</t>
+          <t>1583; 9001</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2656; 10538</t>
+          <t>2568; 10266</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4079; 13735</t>
+          <t>4412; 14443</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6717; 18676</t>
+          <t>6566; 18451</t>
         </is>
       </c>
     </row>
@@ -1632,17 +1632,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2876</t>
+          <t>0; 3188</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1602; 8612</t>
+          <t>1610; 9358</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4664</t>
+          <t>0; 4592</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1652,27 +1652,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>652; 5966</t>
+          <t>658; 6209</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>614; 5196</t>
+          <t>613; 6364</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3172</t>
+          <t>0; 3562</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3040; 11447</t>
+          <t>3188; 12739</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1331; 7573</t>
+          <t>1239; 6992</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1266; 7840</t>
+          <t>1237; 7453</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5024; 15210</t>
+          <t>5259; 15848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4915; 15038</t>
+          <t>5262; 16245</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1317; 7925</t>
+          <t>1299; 8508</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2840; 11182</t>
+          <t>2848; 11619</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2928; 11394</t>
+          <t>2859; 11704</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3691; 12639</t>
+          <t>3505; 12640</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9897; 23270</t>
+          <t>9716; 22836</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10024; 23039</t>
+          <t>9037; 23031</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,86%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,47</t>
+          <t>0,57; 3,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,61</t>
+          <t>0,6; 3,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,11</t>
+          <t>0,6; 3,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,26</t>
+          <t>0,26; 2,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,38</t>
+          <t>0,68; 4,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,57</t>
+          <t>1,5; 5,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,17</t>
+          <t>0,54; 2,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,13</t>
+          <t>0,91; 3,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,65</t>
+          <t>1,31; 3,58</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,5%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,94</t>
+          <t>0,79; 6,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,23</t>
+          <t>0,7; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,56</t>
+          <t>1,67; 9,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,26</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,6</t>
+          <t>1,77; 7,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,99</t>
+          <t>0,43; 4,08</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,12</t>
+          <t>0,37; 2,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,48</t>
+          <t>0,77; 3,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,48</t>
+          <t>0,66; 3,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,35</t>
+          <t>0,36; 2,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,17</t>
+          <t>1,51; 4,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,18</t>
+          <t>1,4; 4,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,77</t>
+          <t>0,48; 1,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,17</t>
+          <t>1,42; 3,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,15</t>
+          <t>1,35; 3,12</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>873</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3845</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2878</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4445</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2417</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3504</t>
+          <t>0; 4348</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3896</t>
+          <t>0; 3901</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>0; 2869</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4087</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4059</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1882</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3901</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7227</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4087</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4059</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>595; 5645</t>
+          <t>1390; 8139</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1458; 7949</t>
+          <t>1450; 8190</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3601; 12912</t>
+          <t>1515; 8989</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1336; 8005</t>
+          <t>596; 4996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1465; 8150</t>
+          <t>1497; 9118</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1583; 9001</t>
+          <t>3784; 13249</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2568; 10266</t>
+          <t>2567; 9766</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4412; 14443</t>
+          <t>4185; 13918</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6566; 18451</t>
+          <t>6637; 18074</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>4120</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1313</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2094</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3188</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1610; 9358</t>
+          <t>653; 5246</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4592</t>
+          <t>614; 5513</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3774</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>658; 6209</t>
+          <t>1428; 8530</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>613; 6364</t>
+          <t>0; 4487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3562</t>
+          <t>0; 3163</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3188; 12739</t>
+          <t>2966; 12068</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1239; 6992</t>
+          <t>762; 7154</t>
         </is>
       </c>
     </row>
@@ -1694,27 +1694,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3387</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9286</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9104</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1237; 7453</t>
+          <t>1331; 7935</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5259; 15848</t>
+          <t>2800; 11351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5262; 16245</t>
+          <t>2440; 11413</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1299; 8508</t>
+          <t>1255; 7349</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2848; 11619</t>
+          <t>5329; 15840</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2859; 11704</t>
+          <t>5089; 15050</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3505; 12640</t>
+          <t>3427; 12413</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9716; 22836</t>
+          <t>10200; 22903</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9037; 23031</t>
+          <t>9859; 22801</t>
         </is>
       </c>
     </row>
